--- a/artfynd/A 55863-2020 artfynd.xlsx
+++ b/artfynd/A 55863-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 55863-2020 artfynd.xlsx
+++ b/artfynd/A 55863-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1018,6 +1018,113 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>68701032</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100371</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Godkänd baserat på observatörens uppgifter</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Söder om stormossen, Ög</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>556518</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6523050</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Skedevi</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2017-09-28</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2017-09-28</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Hilda-Linn Berglund</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Hilda-Linn Berglund</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 55863-2020 artfynd.xlsx
+++ b/artfynd/A 55863-2020 artfynd.xlsx
@@ -1023,7 +1023,7 @@
         <v>68701032</v>
       </c>
       <c r="B5" t="n">
-        <v>100371</v>
+        <v>100379</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
